--- a/fit_video_audit_log.xlsx
+++ b/fit_video_audit_log.xlsx
@@ -425,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -1845,6 +1845,249 @@
         <v>8115.127581834793</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:56:49</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-06-09-07-49-20.fit</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>35367.935</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2057.452404499054</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5</v>
+      </c>
+      <c r="J42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>6570.825501918793</v>
+      </c>
+      <c r="L42" t="n">
+        <v>8698.624155282974</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-09 17:10:28</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-06-09-07-49-20.fit</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>35367.935</v>
+      </c>
+      <c r="D43" t="n">
+        <v>30</v>
+      </c>
+      <c r="G43" t="n">
+        <v>22914.64793777466</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>22950.27482414246</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:43:16</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-06-10-18-40-26.fit</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2499.93</v>
+      </c>
+      <c r="D44" t="n">
+        <v>30</v>
+      </c>
+      <c r="E44" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2502.614182472229</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>442.5015921592712</v>
+      </c>
+      <c r="L44" t="n">
+        <v>2969.631808519363</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-12 15:14:54</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-06-10-18-40-26.fit</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3768.982</v>
+      </c>
+      <c r="D45" t="n">
+        <v>30</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3744.759436607361</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>103.1169934272766</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3876.24118065834</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-13 11:46:26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-06-10-18-40-26.fit</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>7.90202522277832</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-13 11:53:32</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-06-09-07-49-20.fit</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>19224.458</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>468.700302362442</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>507.7284572124481</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-13 12:32:41</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-06-09-07-49-20.fit</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>38995.493</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1018.388791322708</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1056.929676532745</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-13 12:51:11</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-04-11-06-15-17.fit</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>44765.13</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1222.058557033539</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1279.126778125763</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fit_video_audit_log.xlsx
+++ b/fit_video_audit_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -439,7 +439,7 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2421,6 +2421,637 @@
         <v>12348.22965049744</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:38:40</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-06-28-07-33-29.fit</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>15.25091695785522</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-01 16:13:14</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-04-25-10-07-30.fit</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>502.677</v>
+      </c>
+      <c r="D58" t="n">
+        <v>30</v>
+      </c>
+      <c r="E58" t="n">
+        <v>5</v>
+      </c>
+      <c r="F58" t="n">
+        <v>5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>495.7354855537415</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>95.03511762619019</v>
+      </c>
+      <c r="L58" t="n">
+        <v>621.1917645931244</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-01 17:32:41</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-06-28-07-33-29.fit</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>48.51631307601929</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-02 04:01:05</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-04-25-10-07-30.fit</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>502.677</v>
+      </c>
+      <c r="D60" t="n">
+        <v>6</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="n">
+        <v>117.4894781112671</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>25.55897498130798</v>
+      </c>
+      <c r="L60" t="n">
+        <v>215.7993583679199</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-02 16:49:50</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-06-30-18-48-52.fit</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2540.591</v>
+      </c>
+      <c r="D61" t="n">
+        <v>30</v>
+      </c>
+      <c r="E61" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3424.305984258652</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>5</v>
+      </c>
+      <c r="J61" t="n">
+        <v>5</v>
+      </c>
+      <c r="K61" t="n">
+        <v>522.3568849563599</v>
+      </c>
+      <c r="L61" t="n">
+        <v>3966.206719875336</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-03 08:36:07</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-07-01-13-25-22.fit</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1371.668</v>
+      </c>
+      <c r="D62" t="n">
+        <v>30</v>
+      </c>
+      <c r="E62" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1199.293893575668</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>5</v>
+      </c>
+      <c r="J62" t="n">
+        <v>5</v>
+      </c>
+      <c r="K62" t="n">
+        <v>196.8588302135468</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1418.445843696594</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-03 15:15:31</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-07-03-19-18-00.fit</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2033.652</v>
+      </c>
+      <c r="D63" t="n">
+        <v>30</v>
+      </c>
+      <c r="E63" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>5</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1793.492825984955</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>5</v>
+      </c>
+      <c r="J63" t="n">
+        <v>5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>317.2673859596252</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2398.454100608826</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-03 16:53:47</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-07-03-19-18-00.fit</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>295.022</v>
+      </c>
+      <c r="E64" t="n">
+        <v>5</v>
+      </c>
+      <c r="G64" t="n">
+        <v>29.89663290977478</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>83.15789151191711</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:00:59</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-07-03-19-18-00.fit</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>295.022</v>
+      </c>
+      <c r="E65" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" t="n">
+        <v>5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>64.40830087661743</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>89.18947911262512</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:03:54</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-07-03-19-18-00.fit</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2033.652</v>
+      </c>
+      <c r="E66" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" t="n">
+        <v>5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>537.7643201351166</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>554.8830943107605</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-03 17:15:13</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-07-03-19-18-00.fit</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2033.652</v>
+      </c>
+      <c r="E67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>5</v>
+      </c>
+      <c r="G67" t="n">
+        <v>440.6257212162018</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>455.2539441585541</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-04 14:19:52</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-07-04-15-18-11.fit</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>6369.233</v>
+      </c>
+      <c r="D68" t="n">
+        <v>30</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5016.36337351799</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>5</v>
+      </c>
+      <c r="J68" t="n">
+        <v>5</v>
+      </c>
+      <c r="K68" t="n">
+        <v>953.5365755558014</v>
+      </c>
+      <c r="L68" t="n">
+        <v>6021.299674749374</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-04 20:41:34</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-07-04-15-18-11.fit</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>17721.607</v>
+      </c>
+      <c r="D69" t="n">
+        <v>30</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>11345.40590405464</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" t="n">
+        <v>5</v>
+      </c>
+      <c r="J69" t="n">
+        <v>5</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1677.586513757706</v>
+      </c>
+      <c r="L69" t="n">
+        <v>15274.1506254673</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-05 05:42:06</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-07-04-15-18-11.fit</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>17721.607</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>5</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1387.179473638535</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1431.230973005295</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-07 15:33:53</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-07-07-19-21-40.fit</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>3898.418</v>
+      </c>
+      <c r="D71" t="n">
+        <v>30</v>
+      </c>
+      <c r="E71" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" t="n">
+        <v>5</v>
+      </c>
+      <c r="G71" t="n">
+        <v>5943.059675931931</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>5</v>
+      </c>
+      <c r="J71" t="n">
+        <v>5</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1056.120923757553</v>
+      </c>
+      <c r="L71" t="n">
+        <v>7035.11860704422</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:05:26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-07-08-19-29-34.fit</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>4597.173</v>
+      </c>
+      <c r="D72" t="n">
+        <v>30</v>
+      </c>
+      <c r="E72" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" t="n">
+        <v>5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>6498.380990028381</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>5</v>
+      </c>
+      <c r="J72" t="n">
+        <v>5</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1002.115659952164</v>
+      </c>
+      <c r="L72" t="n">
+        <v>7562.684292078018</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-10 15:49:47</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-07-10-19-24-18.fit</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>3906.289</v>
+      </c>
+      <c r="D73" t="n">
+        <v>30</v>
+      </c>
+      <c r="E73" t="n">
+        <v>5</v>
+      </c>
+      <c r="F73" t="n">
+        <v>5</v>
+      </c>
+      <c r="G73" t="n">
+        <v>5908.482997179031</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" t="n">
+        <v>5</v>
+      </c>
+      <c r="J73" t="n">
+        <v>5</v>
+      </c>
+      <c r="K73" t="n">
+        <v>888.8406412601471</v>
+      </c>
+      <c r="L73" t="n">
+        <v>6830.157255649567</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-11 11:58:21</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.002970218658447266</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fit_video_audit_log.xlsx
+++ b/fit_video_audit_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3052,6 +3052,48 @@
         <v>0.002970218658447266</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-12 06:07:19</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-07-12-07-00-05.fit</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6220.426</v>
+      </c>
+      <c r="D75" t="n">
+        <v>30</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>6028.518738508224</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2213.607634782791</v>
+      </c>
+      <c r="L75" t="n">
+        <v>8282.170216083527</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fit_video_audit_log.xlsx
+++ b/fit_video_audit_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3094,6 +3094,84 @@
         <v>8282.170216083527</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-15 05:48:47</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-04-25-10-07-30.fit</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>502.677</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>14.0224781036377</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>30.37969732284546</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-15 05:57:03</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-04-25-10-07-30.fit</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>502.677</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>16.6836359500885</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-15 05:57:27</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-04-25-10-07-30.fit</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>502.677</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>16.83313918113708</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>39.95247077941895</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fit_video_audit_log.xlsx
+++ b/fit_video_audit_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3172,6 +3172,90 @@
         <v>39.95247077941895</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-24 23:50:11</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-07-24-09-29-46.fit</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>5868.587</v>
+      </c>
+      <c r="D79" t="n">
+        <v>30</v>
+      </c>
+      <c r="E79" t="n">
+        <v>5</v>
+      </c>
+      <c r="F79" t="n">
+        <v>5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>5556.599843978882</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>5</v>
+      </c>
+      <c r="J79" t="n">
+        <v>5</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1219.102474689484</v>
+      </c>
+      <c r="L79" t="n">
+        <v>6835.430889368057</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-31 10:55:05</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-07-24-09-29-46.fit</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>3431.587</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="n">
+        <v>293.8357453346252</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>5</v>
+      </c>
+      <c r="J80" t="n">
+        <v>5</v>
+      </c>
+      <c r="K80" t="n">
+        <v>948.4074275493622</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1277.49964594841</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
